--- a/data/Monthly_Attendance.xlsx
+++ b/data/Monthly_Attendance.xlsx
@@ -34,13 +34,16 @@
     </font>
     <font>
       <color rgb="003730A3"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="00991B1B"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00065F46"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -99,13 +102,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,28 +475,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -593,10 +596,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EM001</t>
+          <t>KF001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -674,9 +677,9 @@
           <t>Absent</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>Present</t>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -686,201 +689,302 @@
       </c>
       <c r="S2" s="4" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>IN: 07:28:19
+OUT: 13:40:13</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EM002</t>
+          <t>KF003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Vikas Prajapat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>IN: 07:32:59
+OUT: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KF004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Parth patni</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>IN: 07:55:35
+OUT: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KF002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Ashish Pandey</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EM003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Parth Patani</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>IN: 13:53:43
+OUT: -</t>
         </is>
       </c>
     </row>

--- a/data/Monthly_Attendance.xlsx
+++ b/data/Monthly_Attendance.xlsx
@@ -43,7 +43,7 @@
     <font>
       <b val="1"/>
       <color rgb="00065F46"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -481,22 +481,22 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>KF001</t>
@@ -667,9 +667,10 @@
           <t>Absent</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>IN: Paid Leave
+OUT: Paid Leave</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -689,12 +690,12 @@
       </c>
       <c r="S2" s="4" t="inlineStr">
         <is>
-          <t>IN: 07:28:19
-OUT: 13:40:13</t>
+          <t>IN: Paid Leave
+OUT: Paid Leave</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>KF003</t>
@@ -792,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>KF004</t>
@@ -890,7 +891,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>KF002</t>
@@ -984,7 +985,7 @@
       <c r="S5" s="4" t="inlineStr">
         <is>
           <t>IN: 13:53:43
-OUT: -</t>
+OUT: 14:24:01</t>
         </is>
       </c>
     </row>

--- a/data/Monthly_Attendance.xlsx
+++ b/data/Monthly_Attendance.xlsx
@@ -33,17 +33,17 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="003730A3"/>
       <sz val="9"/>
     </font>
     <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00065F46"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -61,6 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EEF2FF"/>
         <bgColor rgb="00EEF2FF"/>
       </patternFill>
@@ -69,12 +75,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
         <bgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +105,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -475,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -489,14 +492,6 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,82 +512,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>01-Mar</t>
+          <t>01-Apr</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>02-Mar</t>
+          <t>02-Apr</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>03-Mar</t>
+          <t>03-Apr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>04-Mar</t>
+          <t>04-Apr</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>05-Mar</t>
+          <t>05-Apr</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>06-Mar</t>
+          <t>06-Apr</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>07-Mar</t>
+          <t>07-Apr</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>08-Mar</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>09-Mar</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>10-Mar</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>11-Mar</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>12-Mar</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>13-Mar</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>14-Mar</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>15-Mar</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>16-Mar</t>
+          <t>Total Overtime</t>
         </is>
       </c>
     </row>
@@ -614,84 +569,48 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>IN: 09:07:42
+OUT: 17:29:55</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:28
+OUT: 17:32:51</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:04:14
+OUT: -</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:31
+OUT: 17:31:42</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>IN: Paid Leave
-OUT: Paid Leave</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="S2" s="4" t="inlineStr">
-        <is>
-          <t>IN: Paid Leave
-OUT: Paid Leave</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:34
+OUT: 17:32:30</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:02
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -713,193 +632,122 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>IN: 09:06:51
+OUT: 17:30:25</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:07:49
+OUT: 17:29:37</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:12
+OUT: 17:32:06</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:16
+OUT: 17:32:31</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>IN: 07:32:59
-OUT: -</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:48
+OUT: 17:32:44</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:29
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KF004</t>
+          <t>KF002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Parth patni</t>
+          <t>Ashish Pandey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>IN: 09:01:45
+OUT: 17:29:32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:10
+OUT: 17:29:10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:04:02
+OUT: 17:30:46</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Holiday</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>IN: 07:55:35
-OUT: -</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:58
+OUT: 17:31:37</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:39
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KF002</t>
+          <t>KF005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ashish Pandey</t>
+          <t>Vyas vinit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -909,83 +757,664 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>IN: 09:09:37
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:07:31
+OUT: 17:30:09</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:52
+OUT: 17:29:33</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:06:09
+OUT: 17:32:41</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:28
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:20
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KF007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kirit Bhai petal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:09:01
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:12:22
+OUT: 17:32:15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>IN: 17:40:16
+OUT: -</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:10:43
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:19:43
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KF004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Parth Patni</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:07:24
+OUT: 17:30:08</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:44
+OUT: 17:30:52</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:16
+OUT: 17:31:11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:39
+OUT: 17:32:20</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:22
+OUT: 17:29:22</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:06
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KF008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jai Prakash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:09:16
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>IN: 10:11:06
+OUT: -</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:44
+OUT: -</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:58
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>IN: 08:44:55
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KF009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sanjay J parmer Dakor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:16:02
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:07:17
+OUT: -</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>IN: 10:11:54
+OUT: -</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:11:01
+OUT: 17:34:14</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:16:03
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KF010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mahesh parmar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>IN: 10:10:40
+OUT: 17:36:12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:04
+OUT: 17:35:17</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:32
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KF011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sajid bhai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:18:22
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:09:43
+OUT: -</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:06:38
+OUT: 17:31:19</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:32
+OUT: 17:34:25</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:12:21
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:03:15
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KF006</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hitesh bhai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:08:34
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:20:44
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:04:12
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KF013</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Prabhjyot Singh</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:07:08
+OUT: 17:31:25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:41
+OUT: 17:31:20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:04:23
+OUT: 17:29:24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:56
+OUT: 17:31:33</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:00:45
+OUT: 17:29:12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:14
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KF014</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sanjay nasi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>IN: 10:11:20
+OUT: 17:36:23</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Holiday</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>IN: 13:53:43
-OUT: 14:24:01</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:01:13
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:02:20
+OUT: -</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KF012</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Maan Datar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:12:05
+OUT: -</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>IN: 10:11:35
+OUT: -</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>IN: 17:35:54
+OUT: -</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>IN: 09:12:09
+OUT: -</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
